--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_fashion.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_fashion.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="157">
   <si>
     <t>道具id</t>
   </si>
@@ -374,6 +374,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>X</t>
     </r>
     <r>
@@ -431,6 +436,30 @@
     <t>弓箭手</t>
   </si>
   <si>
+    <t>称号：叱咤风云</t>
+  </si>
+  <si>
+    <t>200041#18|206011#18</t>
+  </si>
+  <si>
+    <t>称号：杀戮之王</t>
+  </si>
+  <si>
+    <t>200041#28|206011#28</t>
+  </si>
+  <si>
+    <t>称号：君临天下</t>
+  </si>
+  <si>
+    <t>200041#58|206011#58</t>
+  </si>
+  <si>
+    <t>称号：恶魔猎人</t>
+  </si>
+  <si>
+    <t>200041#98|206011#98</t>
+  </si>
+  <si>
     <t>魔界幻龙皮肤</t>
   </si>
   <si>
@@ -464,16 +493,7 @@
     <t>200011#32|200021#32</t>
   </si>
   <si>
-    <t>称号：杀戮之王</t>
-  </si>
-  <si>
-    <t>称号：君临天下</t>
-  </si>
-  <si>
     <t>206011#20|213021#7|207011#50</t>
-  </si>
-  <si>
-    <t>称号：叱咤风云</t>
   </si>
   <si>
     <t>200011#6|200021#10|207021#500</t>
@@ -729,7 +749,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -751,6 +771,12 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1233,16 +1259,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1251,119 +1274,122 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1406,6 +1432,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1462,19 +1500,19 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1738,7 +1776,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y214"/>
+  <dimension ref="A1:Y222"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -7663,7 +7701,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="209" ht="15" spans="1:11">
+    <row r="209" ht="15" spans="1:12">
       <c r="A209" s="12">
         <v>20931121</v>
       </c>
@@ -7692,7 +7730,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="210" ht="15" spans="1:11">
+    <row r="210" ht="15" spans="1:12">
       <c r="A210" s="12">
         <v>20431221</v>
       </c>
@@ -7721,7 +7759,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="211" ht="15" spans="1:11">
+    <row r="211" ht="15" spans="1:12">
       <c r="A211" s="12">
         <v>20631221</v>
       </c>
@@ -7750,7 +7788,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="212" ht="15" spans="1:11">
+    <row r="212" ht="15" spans="1:12">
       <c r="A212" s="12">
         <v>20731221</v>
       </c>
@@ -7779,7 +7817,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="213" ht="15" spans="1:11">
+    <row r="213" ht="15" spans="1:12">
       <c r="A213" s="12">
         <v>20831221</v>
       </c>
@@ -7808,7 +7846,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="214" ht="15" spans="1:11">
+    <row r="214" ht="15" spans="1:12">
       <c r="A214" s="12">
         <v>20931221</v>
       </c>
@@ -7837,24 +7875,228 @@
         <v>58</v>
       </c>
     </row>
+    <row r="215" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A215" s="18">
+        <v>10101001</v>
+      </c>
+      <c r="B215" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C215">
+        <v>2</v>
+      </c>
+      <c r="G215">
+        <v>1</v>
+      </c>
+      <c r="H215"/>
+      <c r="I215">
+        <v>1</v>
+      </c>
+      <c r="J215" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L215">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="216" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A216" s="18">
+        <v>10101002</v>
+      </c>
+      <c r="B216" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C216">
+        <v>2</v>
+      </c>
+      <c r="G216">
+        <v>1</v>
+      </c>
+      <c r="H216"/>
+      <c r="I216">
+        <v>1</v>
+      </c>
+      <c r="J216" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="L216">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="217" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A217" s="18">
+        <v>10101003</v>
+      </c>
+      <c r="B217" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C217">
+        <v>2</v>
+      </c>
+      <c r="G217">
+        <v>1</v>
+      </c>
+      <c r="H217"/>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="J217" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="L217">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="218" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A218" s="18">
+        <v>10101004</v>
+      </c>
+      <c r="B218" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C218">
+        <v>2</v>
+      </c>
+      <c r="G218">
+        <v>1</v>
+      </c>
+      <c r="H218"/>
+      <c r="I218">
+        <v>1</v>
+      </c>
+      <c r="J218" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="L218">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="219" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A219" s="21">
+        <v>1010100199</v>
+      </c>
+      <c r="B219" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C219">
+        <v>2</v>
+      </c>
+      <c r="G219">
+        <v>1</v>
+      </c>
+      <c r="I219">
+        <v>1</v>
+      </c>
+      <c r="J219" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L219">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="220" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A220" s="21">
+        <v>1010100299</v>
+      </c>
+      <c r="B220" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C220">
+        <v>2</v>
+      </c>
+      <c r="G220">
+        <v>1</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="L220">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="221" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A221" s="21">
+        <v>1010100399</v>
+      </c>
+      <c r="B221" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C221">
+        <v>2</v>
+      </c>
+      <c r="G221">
+        <v>1</v>
+      </c>
+      <c r="I221">
+        <v>1</v>
+      </c>
+      <c r="J221" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="L221">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="222" customFormat="1" ht="16.5" spans="1:12">
+      <c r="A222" s="21">
+        <v>1010100499</v>
+      </c>
+      <c r="B222" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C222">
+        <v>2</v>
+      </c>
+      <c r="G222">
+        <v>1</v>
+      </c>
+      <c r="I222">
+        <v>1</v>
+      </c>
+      <c r="J222" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="L222">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A215">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A219">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A8:A10">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:A15">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A23">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A32:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A216:A218">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A220:A222">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -8059,7 +8301,7 @@
         <v>61300001</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -8071,7 +8313,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M5">
         <v>30</v>
@@ -8082,7 +8324,7 @@
         <v>61300004</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -8094,7 +8336,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M6">
         <v>50</v>
@@ -8105,7 +8347,7 @@
         <v>61300005</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -8117,7 +8359,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="M7">
         <v>50</v>
@@ -8128,7 +8370,7 @@
         <v>61300006</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -8140,7 +8382,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="15" spans="1:25">
@@ -8148,7 +8390,7 @@
         <v>61300007</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -8160,7 +8402,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="15" spans="1:25">
@@ -8168,7 +8410,7 @@
         <v>61300008</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -8180,7 +8422,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" customFormat="1" ht="15" spans="1:25">
@@ -8188,7 +8430,7 @@
         <v>44</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -8203,7 +8445,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" customFormat="1" ht="15" spans="1:25">
@@ -8211,7 +8453,7 @@
         <v>21500003</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -8226,7 +8468,7 @@
         <v>2</v>
       </c>
       <c r="J12" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="15" spans="1:25">
@@ -8234,7 +8476,7 @@
         <v>21500007</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -8249,7 +8491,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L13">
         <v>400</v>
@@ -8260,7 +8502,7 @@
         <v>48</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -8272,7 +8514,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="L14">
         <v>500</v>
@@ -8283,7 +8525,7 @@
         <v>49</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -8295,7 +8537,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="L15">
         <v>500</v>
@@ -8332,7 +8574,7 @@
         <v>21500020</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -8352,7 +8594,7 @@
         <v>21500021</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -8364,7 +8606,7 @@
         <v>1</v>
       </c>
       <c r="J18" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -8375,7 +8617,7 @@
         <v>21500022</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -8387,7 +8629,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -8398,7 +8640,7 @@
         <v>21500023</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -8410,7 +8652,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -8421,7 +8663,7 @@
         <v>21500024</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -8436,7 +8678,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="L21">
         <v>0.35</v>
@@ -8447,7 +8689,7 @@
         <v>21500025</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -8462,7 +8704,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="L22">
         <v>0.35</v>
@@ -8473,7 +8715,7 @@
         <v>21500026</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -8485,7 +8727,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -8496,7 +8738,7 @@
         <v>21500027</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -8508,7 +8750,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -8519,7 +8761,7 @@
         <v>21500028</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -8534,7 +8776,7 @@
         <v>1</v>
       </c>
       <c r="J25" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -8545,7 +8787,7 @@
         <v>61400001</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -8565,7 +8807,7 @@
         <v>61400002</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -8585,7 +8827,7 @@
         <v>61400003</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -8597,7 +8839,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -8608,7 +8850,7 @@
         <v>61400004</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -8620,7 +8862,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -8631,7 +8873,7 @@
         <v>61400005</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -8643,7 +8885,7 @@
         <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -8654,7 +8896,7 @@
         <v>61400006</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -8666,7 +8908,7 @@
         <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L31">
         <v>75</v>
@@ -8677,19 +8919,19 @@
         <v>61400007</v>
       </c>
       <c r="B32" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32" s="12" t="s">
         <v>103</v>
-      </c>
-      <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-      <c r="J32" s="12" t="s">
-        <v>98</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -8700,7 +8942,7 @@
         <v>61400008</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -8712,7 +8954,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -8723,7 +8965,7 @@
         <v>61400009</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C34">
         <v>3</v>
@@ -8735,7 +8977,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="L34">
         <v>100</v>
@@ -8746,7 +8988,7 @@
         <v>20410121</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -8767,7 +9009,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" customFormat="1" ht="15" spans="1:12">
@@ -8775,7 +9017,7 @@
         <v>20610121</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C36">
         <v>4</v>
@@ -8796,7 +9038,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" customFormat="1" ht="15" spans="1:12">
@@ -8804,7 +9046,7 @@
         <v>20710121</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C37">
         <v>4</v>
@@ -8825,7 +9067,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" customFormat="1" ht="15" spans="1:12">
@@ -8833,7 +9075,7 @@
         <v>20810121</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C38">
         <v>4</v>
@@ -8854,7 +9096,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" customFormat="1" ht="15" spans="1:12">
@@ -8862,7 +9104,7 @@
         <v>20910121</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C39">
         <v>4</v>
@@ -8883,7 +9125,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" customFormat="1" ht="15" spans="1:12">
@@ -8891,7 +9133,7 @@
         <v>20410221</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C40">
         <v>4</v>
@@ -8912,7 +9154,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" customFormat="1" ht="15" spans="1:12">
@@ -8920,7 +9162,7 @@
         <v>20610221</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C41">
         <v>4</v>
@@ -8941,7 +9183,7 @@
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" customFormat="1" ht="15" spans="1:12">
@@ -8949,7 +9191,7 @@
         <v>20710221</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C42">
         <v>4</v>
@@ -8970,7 +9212,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" customFormat="1" ht="15" spans="1:12">
@@ -8978,7 +9220,7 @@
         <v>20810221</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C43">
         <v>4</v>
@@ -8999,7 +9241,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" customFormat="1" ht="15" spans="1:12">
@@ -9007,7 +9249,7 @@
         <v>20910221</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C44">
         <v>4</v>
@@ -9028,7 +9270,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" customFormat="1" ht="15" spans="1:12">
@@ -9036,7 +9278,7 @@
         <v>20410321</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -9057,7 +9299,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" customFormat="1" ht="15" spans="1:12">
@@ -9065,7 +9307,7 @@
         <v>20610321</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -9086,7 +9328,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" customFormat="1" ht="15" spans="1:12">
@@ -9094,7 +9336,7 @@
         <v>20710321</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C47">
         <v>4</v>
@@ -9115,7 +9357,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" customFormat="1" ht="15" spans="1:12">
@@ -9123,7 +9365,7 @@
         <v>20810321</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C48">
         <v>4</v>
@@ -9144,7 +9386,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" customFormat="1" ht="15" spans="1:11">
@@ -9152,7 +9394,7 @@
         <v>20910321</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C49">
         <v>4</v>
@@ -9173,7 +9415,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" customFormat="1" ht="15" spans="1:11">
@@ -9181,7 +9423,7 @@
         <v>20410421</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C50">
         <v>4</v>
@@ -9202,7 +9444,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" customFormat="1" ht="15" spans="1:11">
@@ -9210,7 +9452,7 @@
         <v>20610421</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C51">
         <v>4</v>
@@ -9231,7 +9473,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" customFormat="1" ht="15" spans="1:11">
@@ -9239,7 +9481,7 @@
         <v>20710421</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C52">
         <v>4</v>
@@ -9260,7 +9502,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" customFormat="1" ht="15" spans="1:11">
@@ -9268,7 +9510,7 @@
         <v>20810421</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C53">
         <v>4</v>
@@ -9289,7 +9531,7 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" customFormat="1" ht="15" spans="1:11">
@@ -9297,7 +9539,7 @@
         <v>20910421</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C54">
         <v>4</v>
@@ -9318,7 +9560,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" customFormat="1" ht="15" spans="1:11">
@@ -9326,7 +9568,7 @@
         <v>20410521</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C55">
         <v>4</v>
@@ -9347,7 +9589,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" customFormat="1" ht="15" spans="1:11">
@@ -9355,7 +9597,7 @@
         <v>20610521</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C56">
         <v>4</v>
@@ -9376,7 +9618,7 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" customFormat="1" ht="15" spans="1:11">
@@ -9384,7 +9626,7 @@
         <v>20710521</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C57">
         <v>4</v>
@@ -9405,7 +9647,7 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" customFormat="1" ht="15" spans="1:11">
@@ -9413,7 +9655,7 @@
         <v>20810521</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C58">
         <v>4</v>
@@ -9434,7 +9676,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59" customFormat="1" ht="15" spans="1:11">
@@ -9442,7 +9684,7 @@
         <v>20910521</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C59">
         <v>4</v>
@@ -9463,7 +9705,7 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60" customFormat="1" ht="15" spans="1:11">
@@ -9471,7 +9713,7 @@
         <v>20410621</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C60">
         <v>4</v>
@@ -9492,7 +9734,7 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" customFormat="1" ht="15" spans="1:11">
@@ -9500,7 +9742,7 @@
         <v>20610621</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C61">
         <v>4</v>
@@ -9521,7 +9763,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" customFormat="1" ht="15" spans="1:11">
@@ -9529,7 +9771,7 @@
         <v>20710621</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C62">
         <v>4</v>
@@ -9550,7 +9792,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" customFormat="1" ht="15" spans="1:11">
@@ -9558,7 +9800,7 @@
         <v>20810621</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C63">
         <v>4</v>
@@ -9579,7 +9821,7 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" customFormat="1" ht="15" spans="1:11">
@@ -9587,7 +9829,7 @@
         <v>20910621</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C64">
         <v>4</v>
@@ -9608,7 +9850,7 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65" customFormat="1" ht="15" spans="1:11">
@@ -9616,7 +9858,7 @@
         <v>20410721</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C65">
         <v>4</v>
@@ -9637,7 +9879,7 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" customFormat="1" ht="15" spans="1:11">
@@ -9645,7 +9887,7 @@
         <v>20610721</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C66">
         <v>4</v>
@@ -9666,7 +9908,7 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67" customFormat="1" ht="15" spans="1:11">
@@ -9674,7 +9916,7 @@
         <v>20710721</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C67">
         <v>4</v>
@@ -9695,7 +9937,7 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" customFormat="1" ht="15" spans="1:11">
@@ -9703,7 +9945,7 @@
         <v>20810721</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C68">
         <v>4</v>
@@ -9724,7 +9966,7 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" customFormat="1" ht="15" spans="1:11">
@@ -9732,7 +9974,7 @@
         <v>20910721</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C69">
         <v>4</v>
@@ -9753,7 +9995,7 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" customFormat="1" ht="15" spans="1:11">
@@ -9761,7 +10003,7 @@
         <v>20410821</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C70">
         <v>4</v>
@@ -9782,7 +10024,7 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71" customFormat="1" ht="15" spans="1:11">
@@ -9790,7 +10032,7 @@
         <v>20610821</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C71">
         <v>4</v>
@@ -9811,7 +10053,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="72" customFormat="1" ht="15" spans="1:11">
@@ -9819,7 +10061,7 @@
         <v>20710821</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C72">
         <v>4</v>
@@ -9840,7 +10082,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="73" customFormat="1" ht="15" spans="1:11">
@@ -9848,7 +10090,7 @@
         <v>20810821</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C73">
         <v>4</v>
@@ -9869,7 +10111,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="74" customFormat="1" ht="15" spans="1:11">
@@ -9877,7 +10119,7 @@
         <v>20910821</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C74">
         <v>4</v>
@@ -9898,7 +10140,7 @@
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="75" customFormat="1" ht="15" spans="1:11">
@@ -9906,7 +10148,7 @@
         <v>20410921</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C75">
         <v>4</v>
@@ -9927,7 +10169,7 @@
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" customFormat="1" ht="15" spans="1:11">
@@ -9935,7 +10177,7 @@
         <v>20610921</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C76">
         <v>4</v>
@@ -9956,7 +10198,7 @@
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="77" customFormat="1" ht="15" spans="1:11">
@@ -9964,7 +10206,7 @@
         <v>20710921</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C77">
         <v>4</v>
@@ -9985,7 +10227,7 @@
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="78" customFormat="1" ht="15" spans="1:11">
@@ -9993,7 +10235,7 @@
         <v>20810921</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C78">
         <v>4</v>
@@ -10014,7 +10256,7 @@
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="79" customFormat="1" ht="15" spans="1:11">
@@ -10022,7 +10264,7 @@
         <v>20910921</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C79">
         <v>4</v>
@@ -10043,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="80" customFormat="1" ht="15" spans="1:11">
@@ -10051,7 +10293,7 @@
         <v>20411021</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C80">
         <v>4</v>
@@ -10072,7 +10314,7 @@
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="81" customFormat="1" ht="15" spans="1:11">
@@ -10080,7 +10322,7 @@
         <v>20611021</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C81">
         <v>4</v>
@@ -10101,7 +10343,7 @@
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="82" customFormat="1" ht="15" spans="1:11">
@@ -10109,7 +10351,7 @@
         <v>20711021</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C82">
         <v>4</v>
@@ -10130,7 +10372,7 @@
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="83" customFormat="1" ht="15" spans="1:11">
@@ -10138,7 +10380,7 @@
         <v>20811021</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C83">
         <v>4</v>
@@ -10159,7 +10401,7 @@
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="84" customFormat="1" ht="15" spans="1:11">
@@ -10167,7 +10409,7 @@
         <v>20911021</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C84">
         <v>4</v>
@@ -10188,7 +10430,7 @@
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="85" customFormat="1" ht="15" spans="1:11">
@@ -10196,7 +10438,7 @@
         <v>20411121</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C85">
         <v>4</v>
@@ -10217,7 +10459,7 @@
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="86" customFormat="1" ht="15" spans="1:11">
@@ -10225,7 +10467,7 @@
         <v>20611121</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C86">
         <v>4</v>
@@ -10246,7 +10488,7 @@
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="87" customFormat="1" ht="15" spans="1:11">
@@ -10254,7 +10496,7 @@
         <v>20711121</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C87">
         <v>4</v>
@@ -10275,7 +10517,7 @@
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="88" customFormat="1" ht="15" spans="1:11">
@@ -10283,7 +10525,7 @@
         <v>20811121</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C88">
         <v>4</v>
@@ -10304,7 +10546,7 @@
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="89" customFormat="1" ht="15" spans="1:11">
@@ -10312,7 +10554,7 @@
         <v>20911121</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C89">
         <v>4</v>
@@ -10333,7 +10575,7 @@
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="90" customFormat="1" ht="15" spans="1:11">
@@ -10341,7 +10583,7 @@
         <v>20411221</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C90">
         <v>4</v>
@@ -10362,7 +10604,7 @@
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="91" customFormat="1" ht="15" spans="1:11">
@@ -10370,7 +10612,7 @@
         <v>20611221</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C91">
         <v>4</v>
@@ -10391,7 +10633,7 @@
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="92" customFormat="1" ht="15" spans="1:11">
@@ -10399,7 +10641,7 @@
         <v>20711221</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C92">
         <v>4</v>
@@ -10420,7 +10662,7 @@
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="93" customFormat="1" ht="15" spans="1:11">
@@ -10428,7 +10670,7 @@
         <v>20811221</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C93">
         <v>4</v>
@@ -10449,7 +10691,7 @@
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="94" customFormat="1" ht="15" spans="1:11">
@@ -10457,7 +10699,7 @@
         <v>20911221</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C94">
         <v>4</v>
@@ -10478,7 +10720,7 @@
         <v>1</v>
       </c>
       <c r="K94" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="95" customFormat="1" ht="15" spans="1:11">
@@ -10486,7 +10728,7 @@
         <v>20420121</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C95">
         <v>4</v>
@@ -10507,7 +10749,7 @@
         <v>1</v>
       </c>
       <c r="K95" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="96" customFormat="1" ht="15" spans="1:11">
@@ -10515,7 +10757,7 @@
         <v>20620121</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C96">
         <v>4</v>
@@ -10536,7 +10778,7 @@
         <v>1</v>
       </c>
       <c r="K96" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="97" customFormat="1" ht="15" spans="1:11">
@@ -10544,7 +10786,7 @@
         <v>20720121</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C97">
         <v>4</v>
@@ -10565,7 +10807,7 @@
         <v>1</v>
       </c>
       <c r="K97" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="98" customFormat="1" ht="15" spans="1:11">
@@ -10573,7 +10815,7 @@
         <v>20820121</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C98">
         <v>4</v>
@@ -10594,7 +10836,7 @@
         <v>1</v>
       </c>
       <c r="K98" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="99" customFormat="1" ht="15" spans="1:11">
@@ -10602,7 +10844,7 @@
         <v>20920121</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C99">
         <v>4</v>
@@ -10623,7 +10865,7 @@
         <v>1</v>
       </c>
       <c r="K99" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="100" customFormat="1" ht="15" spans="1:11">
@@ -10631,7 +10873,7 @@
         <v>20420221</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C100">
         <v>4</v>
@@ -10652,7 +10894,7 @@
         <v>1</v>
       </c>
       <c r="K100" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="101" customFormat="1" ht="15" spans="1:11">
@@ -10660,7 +10902,7 @@
         <v>20620221</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C101">
         <v>4</v>
@@ -10681,7 +10923,7 @@
         <v>1</v>
       </c>
       <c r="K101" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="102" customFormat="1" ht="15" spans="1:11">
@@ -10689,7 +10931,7 @@
         <v>20720221</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C102">
         <v>4</v>
@@ -10710,7 +10952,7 @@
         <v>1</v>
       </c>
       <c r="K102" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="103" customFormat="1" ht="15" spans="1:11">
@@ -10718,7 +10960,7 @@
         <v>20820221</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C103">
         <v>4</v>
@@ -10739,7 +10981,7 @@
         <v>1</v>
       </c>
       <c r="K103" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104" customFormat="1" ht="15" spans="1:11">
@@ -10747,7 +10989,7 @@
         <v>20920221</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C104">
         <v>4</v>
@@ -10768,7 +11010,7 @@
         <v>1</v>
       </c>
       <c r="K104" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" customFormat="1" ht="15" spans="1:11">
@@ -10776,7 +11018,7 @@
         <v>20420321</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C105">
         <v>4</v>
@@ -10797,7 +11039,7 @@
         <v>1</v>
       </c>
       <c r="K105" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="106" customFormat="1" ht="15" spans="1:11">
@@ -10805,7 +11047,7 @@
         <v>20620321</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C106">
         <v>4</v>
@@ -10826,7 +11068,7 @@
         <v>1</v>
       </c>
       <c r="K106" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="107" customFormat="1" ht="15" spans="1:11">
@@ -10834,7 +11076,7 @@
         <v>20720321</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C107">
         <v>4</v>
@@ -10855,7 +11097,7 @@
         <v>1</v>
       </c>
       <c r="K107" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="108" customFormat="1" ht="15" spans="1:11">
@@ -10863,7 +11105,7 @@
         <v>20820321</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C108">
         <v>4</v>
@@ -10884,7 +11126,7 @@
         <v>1</v>
       </c>
       <c r="K108" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="109" customFormat="1" ht="15" spans="1:11">
@@ -10892,7 +11134,7 @@
         <v>20920321</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C109">
         <v>4</v>
@@ -10913,7 +11155,7 @@
         <v>1</v>
       </c>
       <c r="K109" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="110" customFormat="1" ht="15" spans="1:11">
@@ -10921,7 +11163,7 @@
         <v>20420421</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C110">
         <v>4</v>
@@ -10942,7 +11184,7 @@
         <v>1</v>
       </c>
       <c r="K110" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="111" customFormat="1" ht="15" spans="1:11">
@@ -10950,7 +11192,7 @@
         <v>20620421</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C111">
         <v>4</v>
@@ -10971,7 +11213,7 @@
         <v>1</v>
       </c>
       <c r="K111" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="112" customFormat="1" ht="15" spans="1:11">
@@ -10979,7 +11221,7 @@
         <v>20720421</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C112">
         <v>4</v>
@@ -11000,7 +11242,7 @@
         <v>1</v>
       </c>
       <c r="K112" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="113" customFormat="1" ht="15" spans="1:11">
@@ -11008,7 +11250,7 @@
         <v>20820421</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C113">
         <v>4</v>
@@ -11029,7 +11271,7 @@
         <v>1</v>
       </c>
       <c r="K113" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="114" customFormat="1" ht="15" spans="1:11">
@@ -11037,7 +11279,7 @@
         <v>20920421</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C114">
         <v>4</v>
@@ -11058,7 +11300,7 @@
         <v>1</v>
       </c>
       <c r="K114" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="115" customFormat="1" ht="15" spans="1:11">
@@ -11066,7 +11308,7 @@
         <v>20420521</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C115">
         <v>4</v>
@@ -11087,7 +11329,7 @@
         <v>1</v>
       </c>
       <c r="K115" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="116" customFormat="1" ht="15" spans="1:11">
@@ -11095,7 +11337,7 @@
         <v>20620521</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C116">
         <v>4</v>
@@ -11116,7 +11358,7 @@
         <v>1</v>
       </c>
       <c r="K116" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="117" customFormat="1" ht="15" spans="1:11">
@@ -11124,7 +11366,7 @@
         <v>20720521</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C117">
         <v>4</v>
@@ -11145,7 +11387,7 @@
         <v>1</v>
       </c>
       <c r="K117" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="118" customFormat="1" ht="15" spans="1:11">
@@ -11153,7 +11395,7 @@
         <v>20820521</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C118">
         <v>4</v>
@@ -11174,7 +11416,7 @@
         <v>1</v>
       </c>
       <c r="K118" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="119" customFormat="1" ht="15" spans="1:11">
@@ -11182,7 +11424,7 @@
         <v>20920521</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C119">
         <v>4</v>
@@ -11203,7 +11445,7 @@
         <v>1</v>
       </c>
       <c r="K119" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="120" customFormat="1" ht="15" spans="1:11">
@@ -11211,7 +11453,7 @@
         <v>20420621</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C120">
         <v>4</v>
@@ -11232,7 +11474,7 @@
         <v>1</v>
       </c>
       <c r="K120" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="121" customFormat="1" ht="15" spans="1:11">
@@ -11240,7 +11482,7 @@
         <v>20620621</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C121">
         <v>4</v>
@@ -11261,7 +11503,7 @@
         <v>1</v>
       </c>
       <c r="K121" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="122" customFormat="1" ht="15" spans="1:11">
@@ -11269,7 +11511,7 @@
         <v>20720621</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C122">
         <v>4</v>
@@ -11290,7 +11532,7 @@
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="123" customFormat="1" ht="15" spans="1:11">
@@ -11298,7 +11540,7 @@
         <v>20820621</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C123">
         <v>4</v>
@@ -11319,7 +11561,7 @@
         <v>1</v>
       </c>
       <c r="K123" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="124" customFormat="1" ht="15" spans="1:11">
@@ -11327,7 +11569,7 @@
         <v>20920621</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C124">
         <v>4</v>
@@ -11348,7 +11590,7 @@
         <v>1</v>
       </c>
       <c r="K124" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="125" customFormat="1" ht="15" spans="1:11">
@@ -11356,7 +11598,7 @@
         <v>20420721</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C125">
         <v>4</v>
@@ -11377,7 +11619,7 @@
         <v>1</v>
       </c>
       <c r="K125" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="126" customFormat="1" ht="15" spans="1:11">
@@ -11385,7 +11627,7 @@
         <v>20620721</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C126">
         <v>4</v>
@@ -11406,7 +11648,7 @@
         <v>1</v>
       </c>
       <c r="K126" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="127" customFormat="1" ht="15" spans="1:11">
@@ -11414,7 +11656,7 @@
         <v>20720721</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C127">
         <v>4</v>
@@ -11435,7 +11677,7 @@
         <v>1</v>
       </c>
       <c r="K127" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="128" customFormat="1" ht="15" spans="1:11">
@@ -11443,7 +11685,7 @@
         <v>20820721</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C128">
         <v>4</v>
@@ -11464,7 +11706,7 @@
         <v>1</v>
       </c>
       <c r="K128" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="129" customFormat="1" ht="15" spans="1:11">
@@ -11472,7 +11714,7 @@
         <v>20920721</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C129">
         <v>4</v>
@@ -11493,7 +11735,7 @@
         <v>1</v>
       </c>
       <c r="K129" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="130" customFormat="1" ht="15" spans="1:11">
@@ -11501,7 +11743,7 @@
         <v>20420821</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C130">
         <v>4</v>
@@ -11522,7 +11764,7 @@
         <v>1</v>
       </c>
       <c r="K130" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="131" customFormat="1" ht="15" spans="1:11">
@@ -11530,7 +11772,7 @@
         <v>20620821</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C131">
         <v>4</v>
@@ -11551,7 +11793,7 @@
         <v>1</v>
       </c>
       <c r="K131" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="132" customFormat="1" ht="15" spans="1:11">
@@ -11559,7 +11801,7 @@
         <v>20720821</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C132">
         <v>4</v>
@@ -11580,7 +11822,7 @@
         <v>1</v>
       </c>
       <c r="K132" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="133" customFormat="1" ht="15" spans="1:11">
@@ -11588,7 +11830,7 @@
         <v>20820821</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C133">
         <v>4</v>
@@ -11609,7 +11851,7 @@
         <v>1</v>
       </c>
       <c r="K133" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="134" customFormat="1" ht="15" spans="1:11">
@@ -11617,7 +11859,7 @@
         <v>20920821</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C134">
         <v>4</v>
@@ -11638,7 +11880,7 @@
         <v>1</v>
       </c>
       <c r="K134" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="135" customFormat="1" ht="15" spans="1:11">
@@ -11646,7 +11888,7 @@
         <v>20420921</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C135">
         <v>4</v>
@@ -11667,7 +11909,7 @@
         <v>1</v>
       </c>
       <c r="K135" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="136" customFormat="1" ht="15" spans="1:11">
@@ -11675,7 +11917,7 @@
         <v>20620921</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C136">
         <v>4</v>
@@ -11696,7 +11938,7 @@
         <v>1</v>
       </c>
       <c r="K136" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="137" customFormat="1" ht="15" spans="1:11">
@@ -11704,7 +11946,7 @@
         <v>20720921</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C137">
         <v>4</v>
@@ -11725,7 +11967,7 @@
         <v>1</v>
       </c>
       <c r="K137" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="138" customFormat="1" ht="15" spans="1:11">
@@ -11733,7 +11975,7 @@
         <v>20820921</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C138">
         <v>4</v>
@@ -11754,7 +11996,7 @@
         <v>1</v>
       </c>
       <c r="K138" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="139" customFormat="1" ht="15" spans="1:11">
@@ -11762,7 +12004,7 @@
         <v>20920921</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C139">
         <v>4</v>
@@ -11783,7 +12025,7 @@
         <v>1</v>
       </c>
       <c r="K139" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="140" customFormat="1" ht="15" spans="1:11">
@@ -11791,7 +12033,7 @@
         <v>20421021</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C140">
         <v>4</v>
@@ -11812,7 +12054,7 @@
         <v>1</v>
       </c>
       <c r="K140" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="141" customFormat="1" ht="15" spans="1:11">
@@ -11820,7 +12062,7 @@
         <v>20621021</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C141">
         <v>4</v>
@@ -11841,7 +12083,7 @@
         <v>1</v>
       </c>
       <c r="K141" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="142" customFormat="1" ht="15" spans="1:11">
@@ -11849,7 +12091,7 @@
         <v>20721021</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C142">
         <v>4</v>
@@ -11870,7 +12112,7 @@
         <v>1</v>
       </c>
       <c r="K142" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="143" customFormat="1" ht="15" spans="1:11">
@@ -11878,7 +12120,7 @@
         <v>20821021</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C143">
         <v>4</v>
@@ -11899,7 +12141,7 @@
         <v>1</v>
       </c>
       <c r="K143" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="144" customFormat="1" ht="15" spans="1:11">
@@ -11907,7 +12149,7 @@
         <v>20921021</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C144">
         <v>4</v>
@@ -11928,7 +12170,7 @@
         <v>1</v>
       </c>
       <c r="K144" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="145" customFormat="1" ht="15" spans="1:11">
@@ -11936,7 +12178,7 @@
         <v>20421121</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C145">
         <v>4</v>
@@ -11957,7 +12199,7 @@
         <v>1</v>
       </c>
       <c r="K145" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="146" customFormat="1" ht="15" spans="1:11">
@@ -11965,7 +12207,7 @@
         <v>20621121</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C146">
         <v>4</v>
@@ -11986,7 +12228,7 @@
         <v>1</v>
       </c>
       <c r="K146" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="147" customFormat="1" ht="15" spans="1:11">
@@ -11994,7 +12236,7 @@
         <v>20721121</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C147">
         <v>4</v>
@@ -12015,7 +12257,7 @@
         <v>1</v>
       </c>
       <c r="K147" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="148" customFormat="1" ht="15" spans="1:11">
@@ -12023,7 +12265,7 @@
         <v>20821121</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C148">
         <v>4</v>
@@ -12044,7 +12286,7 @@
         <v>1</v>
       </c>
       <c r="K148" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="149" customFormat="1" ht="15" spans="1:11">
@@ -12052,7 +12294,7 @@
         <v>20921121</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C149">
         <v>4</v>
@@ -12073,7 +12315,7 @@
         <v>1</v>
       </c>
       <c r="K149" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="150" customFormat="1" ht="15" spans="1:11">
@@ -12081,7 +12323,7 @@
         <v>20421221</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C150">
         <v>4</v>
@@ -12102,7 +12344,7 @@
         <v>1</v>
       </c>
       <c r="K150" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="151" customFormat="1" ht="15" spans="1:11">
@@ -12110,7 +12352,7 @@
         <v>20621221</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C151">
         <v>4</v>
@@ -12131,7 +12373,7 @@
         <v>1</v>
       </c>
       <c r="K151" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="152" customFormat="1" ht="15" spans="1:11">
@@ -12139,7 +12381,7 @@
         <v>20721221</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C152">
         <v>4</v>
@@ -12160,7 +12402,7 @@
         <v>1</v>
       </c>
       <c r="K152" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="153" customFormat="1" ht="15" spans="1:11">
@@ -12168,7 +12410,7 @@
         <v>20821221</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C153">
         <v>4</v>
@@ -12189,7 +12431,7 @@
         <v>1</v>
       </c>
       <c r="K153" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="154" customFormat="1" ht="15" spans="1:11">
@@ -12197,7 +12439,7 @@
         <v>20921221</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C154">
         <v>4</v>
@@ -12218,7 +12460,7 @@
         <v>1</v>
       </c>
       <c r="K154" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="155" customFormat="1" ht="15" spans="1:11">
@@ -12226,7 +12468,7 @@
         <v>20430121</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C155">
         <v>4</v>
@@ -12247,7 +12489,7 @@
         <v>1</v>
       </c>
       <c r="K155" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="156" customFormat="1" ht="15" spans="1:11">
@@ -12255,7 +12497,7 @@
         <v>20630121</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C156">
         <v>4</v>
@@ -12276,7 +12518,7 @@
         <v>1</v>
       </c>
       <c r="K156" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="157" customFormat="1" ht="15" spans="1:11">
@@ -12284,7 +12526,7 @@
         <v>20730121</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C157">
         <v>4</v>
@@ -12305,7 +12547,7 @@
         <v>1</v>
       </c>
       <c r="K157" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="158" customFormat="1" ht="15" spans="1:11">
@@ -12313,7 +12555,7 @@
         <v>20830121</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C158">
         <v>4</v>
@@ -12334,7 +12576,7 @@
         <v>1</v>
       </c>
       <c r="K158" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="159" customFormat="1" ht="15" spans="1:11">
@@ -12342,7 +12584,7 @@
         <v>20930121</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C159">
         <v>4</v>
@@ -12363,7 +12605,7 @@
         <v>1</v>
       </c>
       <c r="K159" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="160" customFormat="1" ht="15" spans="1:11">
@@ -12371,7 +12613,7 @@
         <v>20430221</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C160">
         <v>4</v>
@@ -12392,7 +12634,7 @@
         <v>1</v>
       </c>
       <c r="K160" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="161" customFormat="1" ht="15" spans="1:11">
@@ -12400,7 +12642,7 @@
         <v>20630221</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C161">
         <v>4</v>
@@ -12421,7 +12663,7 @@
         <v>1</v>
       </c>
       <c r="K161" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="162" customFormat="1" ht="15" spans="1:11">
@@ -12429,7 +12671,7 @@
         <v>20730221</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C162">
         <v>4</v>
@@ -12450,7 +12692,7 @@
         <v>1</v>
       </c>
       <c r="K162" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="163" customFormat="1" ht="15" spans="1:11">
@@ -12458,7 +12700,7 @@
         <v>20830221</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C163">
         <v>4</v>
@@ -12479,7 +12721,7 @@
         <v>1</v>
       </c>
       <c r="K163" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="164" customFormat="1" ht="15" spans="1:11">
@@ -12487,7 +12729,7 @@
         <v>20930221</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C164">
         <v>4</v>
@@ -12508,7 +12750,7 @@
         <v>1</v>
       </c>
       <c r="K164" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="165" customFormat="1" ht="15" spans="1:11">
@@ -12516,7 +12758,7 @@
         <v>20430321</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C165">
         <v>4</v>
@@ -12537,7 +12779,7 @@
         <v>1</v>
       </c>
       <c r="K165" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="166" customFormat="1" ht="15" spans="1:11">
@@ -12545,7 +12787,7 @@
         <v>20630321</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C166">
         <v>4</v>
@@ -12566,7 +12808,7 @@
         <v>1</v>
       </c>
       <c r="K166" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="167" customFormat="1" ht="15" spans="1:11">
@@ -12574,7 +12816,7 @@
         <v>20730321</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C167">
         <v>4</v>
@@ -12595,7 +12837,7 @@
         <v>1</v>
       </c>
       <c r="K167" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="168" customFormat="1" ht="15" spans="1:11">
@@ -12603,7 +12845,7 @@
         <v>20830321</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C168">
         <v>4</v>
@@ -12624,7 +12866,7 @@
         <v>1</v>
       </c>
       <c r="K168" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="169" customFormat="1" ht="15" spans="1:11">
@@ -12632,7 +12874,7 @@
         <v>20930321</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C169">
         <v>4</v>
@@ -12653,7 +12895,7 @@
         <v>1</v>
       </c>
       <c r="K169" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="170" customFormat="1" ht="15" spans="1:11">
@@ -12661,7 +12903,7 @@
         <v>20430421</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C170">
         <v>4</v>
@@ -12682,7 +12924,7 @@
         <v>1</v>
       </c>
       <c r="K170" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="171" customFormat="1" ht="15" spans="1:11">
@@ -12690,7 +12932,7 @@
         <v>20630421</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C171">
         <v>4</v>
@@ -12711,7 +12953,7 @@
         <v>1</v>
       </c>
       <c r="K171" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="172" customFormat="1" ht="15" spans="1:11">
@@ -12719,7 +12961,7 @@
         <v>20730421</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C172">
         <v>4</v>
@@ -12740,7 +12982,7 @@
         <v>1</v>
       </c>
       <c r="K172" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="173" customFormat="1" ht="15" spans="1:11">
@@ -12748,7 +12990,7 @@
         <v>20830421</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C173">
         <v>4</v>
@@ -12769,7 +13011,7 @@
         <v>1</v>
       </c>
       <c r="K173" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="174" customFormat="1" ht="15" spans="1:11">
@@ -12777,7 +13019,7 @@
         <v>20930421</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C174">
         <v>4</v>
@@ -12798,7 +13040,7 @@
         <v>1</v>
       </c>
       <c r="K174" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="175" customFormat="1" ht="15" spans="1:11">
@@ -12806,7 +13048,7 @@
         <v>20430521</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C175">
         <v>4</v>
@@ -12827,7 +13069,7 @@
         <v>1</v>
       </c>
       <c r="K175" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="176" customFormat="1" ht="15" spans="1:11">
@@ -12835,7 +13077,7 @@
         <v>20630521</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C176">
         <v>4</v>
@@ -12856,7 +13098,7 @@
         <v>1</v>
       </c>
       <c r="K176" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="177" customFormat="1" ht="15" spans="1:11">
@@ -12864,7 +13106,7 @@
         <v>20730521</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C177">
         <v>4</v>
@@ -12885,7 +13127,7 @@
         <v>1</v>
       </c>
       <c r="K177" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="178" customFormat="1" ht="15" spans="1:11">
@@ -12893,7 +13135,7 @@
         <v>20830521</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C178">
         <v>4</v>
@@ -12914,7 +13156,7 @@
         <v>1</v>
       </c>
       <c r="K178" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="179" customFormat="1" ht="15" spans="1:11">
@@ -12922,7 +13164,7 @@
         <v>20930521</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C179">
         <v>4</v>
@@ -12943,7 +13185,7 @@
         <v>1</v>
       </c>
       <c r="K179" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="180" customFormat="1" ht="15" spans="1:11">
@@ -12951,7 +13193,7 @@
         <v>20430621</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C180">
         <v>4</v>
@@ -12972,7 +13214,7 @@
         <v>1</v>
       </c>
       <c r="K180" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="181" customFormat="1" ht="15" spans="1:11">
@@ -12980,7 +13222,7 @@
         <v>20630621</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C181">
         <v>4</v>
@@ -13001,7 +13243,7 @@
         <v>1</v>
       </c>
       <c r="K181" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="182" customFormat="1" ht="15" spans="1:11">
@@ -13009,7 +13251,7 @@
         <v>20730621</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C182">
         <v>4</v>
@@ -13030,7 +13272,7 @@
         <v>1</v>
       </c>
       <c r="K182" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="183" customFormat="1" ht="15" spans="1:11">
@@ -13038,7 +13280,7 @@
         <v>20830621</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C183">
         <v>4</v>
@@ -13059,7 +13301,7 @@
         <v>1</v>
       </c>
       <c r="K183" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="184" customFormat="1" ht="15" spans="1:11">
@@ -13067,7 +13309,7 @@
         <v>20930621</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C184">
         <v>4</v>
@@ -13088,7 +13330,7 @@
         <v>1</v>
       </c>
       <c r="K184" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="185" customFormat="1" ht="15" spans="1:11">
@@ -13096,7 +13338,7 @@
         <v>20430721</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C185">
         <v>4</v>
@@ -13117,7 +13359,7 @@
         <v>1</v>
       </c>
       <c r="K185" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="186" customFormat="1" ht="15" spans="1:11">
@@ -13125,7 +13367,7 @@
         <v>20630721</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C186">
         <v>4</v>
@@ -13146,7 +13388,7 @@
         <v>1</v>
       </c>
       <c r="K186" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="187" customFormat="1" ht="15" spans="1:11">
@@ -13154,7 +13396,7 @@
         <v>20730721</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C187">
         <v>4</v>
@@ -13175,7 +13417,7 @@
         <v>1</v>
       </c>
       <c r="K187" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="188" customFormat="1" ht="15" spans="1:11">
@@ -13183,7 +13425,7 @@
         <v>20830721</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C188">
         <v>4</v>
@@ -13204,7 +13446,7 @@
         <v>1</v>
       </c>
       <c r="K188" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="189" customFormat="1" ht="15" spans="1:11">
@@ -13212,7 +13454,7 @@
         <v>20930721</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C189">
         <v>4</v>
@@ -13233,7 +13475,7 @@
         <v>1</v>
       </c>
       <c r="K189" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="190" customFormat="1" ht="15" spans="1:11">
@@ -13241,7 +13483,7 @@
         <v>20430821</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C190">
         <v>4</v>
@@ -13262,7 +13504,7 @@
         <v>1</v>
       </c>
       <c r="K190" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="191" customFormat="1" ht="15" spans="1:11">
@@ -13270,7 +13512,7 @@
         <v>20630821</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C191">
         <v>4</v>
@@ -13291,7 +13533,7 @@
         <v>1</v>
       </c>
       <c r="K191" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="192" customFormat="1" ht="15" spans="1:11">
@@ -13299,7 +13541,7 @@
         <v>20730821</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C192">
         <v>4</v>
@@ -13320,7 +13562,7 @@
         <v>1</v>
       </c>
       <c r="K192" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="193" customFormat="1" ht="15" spans="1:11">
@@ -13328,7 +13570,7 @@
         <v>20830821</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C193">
         <v>4</v>
@@ -13349,7 +13591,7 @@
         <v>1</v>
       </c>
       <c r="K193" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="194" customFormat="1" ht="15" spans="1:11">
@@ -13357,7 +13599,7 @@
         <v>20930821</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C194">
         <v>4</v>
@@ -13378,7 +13620,7 @@
         <v>1</v>
       </c>
       <c r="K194" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="195" customFormat="1" ht="15" spans="1:11">
@@ -13386,7 +13628,7 @@
         <v>20430921</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C195">
         <v>4</v>
@@ -13407,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="K195" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="196" customFormat="1" ht="15" spans="1:11">
@@ -13415,7 +13657,7 @@
         <v>20630921</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C196">
         <v>4</v>
@@ -13436,7 +13678,7 @@
         <v>1</v>
       </c>
       <c r="K196" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="197" customFormat="1" ht="15" spans="1:11">
@@ -13444,7 +13686,7 @@
         <v>20730921</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C197">
         <v>4</v>
@@ -13465,7 +13707,7 @@
         <v>1</v>
       </c>
       <c r="K197" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="198" customFormat="1" ht="15" spans="1:11">
@@ -13473,7 +13715,7 @@
         <v>20830921</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C198">
         <v>4</v>
@@ -13494,7 +13736,7 @@
         <v>1</v>
       </c>
       <c r="K198" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="199" customFormat="1" ht="15" spans="1:11">
@@ -13502,7 +13744,7 @@
         <v>20930921</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C199">
         <v>4</v>
@@ -13523,7 +13765,7 @@
         <v>1</v>
       </c>
       <c r="K199" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="200" customFormat="1" ht="15" spans="1:11">
@@ -13531,7 +13773,7 @@
         <v>20431021</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C200">
         <v>4</v>
@@ -13552,7 +13794,7 @@
         <v>1</v>
       </c>
       <c r="K200" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="201" customFormat="1" ht="15" spans="1:11">
@@ -13560,7 +13802,7 @@
         <v>20631021</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C201">
         <v>4</v>
@@ -13581,7 +13823,7 @@
         <v>1</v>
       </c>
       <c r="K201" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="202" customFormat="1" ht="15" spans="1:11">
@@ -13589,7 +13831,7 @@
         <v>20731021</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C202">
         <v>4</v>
@@ -13610,7 +13852,7 @@
         <v>1</v>
       </c>
       <c r="K202" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="203" customFormat="1" ht="15" spans="1:11">
@@ -13618,7 +13860,7 @@
         <v>20831021</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C203">
         <v>4</v>
@@ -13639,7 +13881,7 @@
         <v>1</v>
       </c>
       <c r="K203" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="204" customFormat="1" ht="15" spans="1:11">
@@ -13647,7 +13889,7 @@
         <v>20931021</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C204">
         <v>4</v>
@@ -13668,7 +13910,7 @@
         <v>1</v>
       </c>
       <c r="K204" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="205" customFormat="1" ht="15" spans="1:11">
@@ -13676,7 +13918,7 @@
         <v>20431121</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C205">
         <v>4</v>
@@ -13697,7 +13939,7 @@
         <v>1</v>
       </c>
       <c r="K205" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="206" customFormat="1" ht="15" spans="1:11">
@@ -13705,7 +13947,7 @@
         <v>20631121</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C206">
         <v>4</v>
@@ -13726,7 +13968,7 @@
         <v>1</v>
       </c>
       <c r="K206" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="207" customFormat="1" ht="15" spans="1:11">
@@ -13734,7 +13976,7 @@
         <v>20731121</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C207">
         <v>4</v>
@@ -13755,7 +13997,7 @@
         <v>1</v>
       </c>
       <c r="K207" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="208" customFormat="1" ht="15" spans="1:11">
@@ -13763,7 +14005,7 @@
         <v>20831121</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C208">
         <v>4</v>
@@ -13784,7 +14026,7 @@
         <v>1</v>
       </c>
       <c r="K208" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="209" customFormat="1" ht="15" spans="1:11">
@@ -13792,7 +14034,7 @@
         <v>20931121</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C209">
         <v>4</v>
@@ -13813,7 +14055,7 @@
         <v>1</v>
       </c>
       <c r="K209" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="210" customFormat="1" ht="15" spans="1:11">
@@ -13821,7 +14063,7 @@
         <v>20431221</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C210">
         <v>4</v>
@@ -13842,7 +14084,7 @@
         <v>1</v>
       </c>
       <c r="K210" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="211" customFormat="1" ht="15" spans="1:11">
@@ -13850,7 +14092,7 @@
         <v>20631221</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C211">
         <v>4</v>
@@ -13871,7 +14113,7 @@
         <v>1</v>
       </c>
       <c r="K211" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="212" customFormat="1" ht="15" spans="1:11">
@@ -13879,7 +14121,7 @@
         <v>20731221</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -13900,7 +14142,7 @@
         <v>1</v>
       </c>
       <c r="K212" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="213" customFormat="1" ht="15" spans="1:11">
@@ -13908,7 +14150,7 @@
         <v>20831221</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -13929,7 +14171,7 @@
         <v>1</v>
       </c>
       <c r="K213" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="214" customFormat="1" ht="15" spans="1:11">
@@ -13937,7 +14179,7 @@
         <v>20931221</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C214">
         <v>4</v>
@@ -13958,27 +14200,27 @@
         <v>1</v>
       </c>
       <c r="K214" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A8:A10">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14:A15">
-    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A23">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A25">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A32:A34">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
